--- a/data/industry/CFM/Flash Card.xlsx
+++ b/data/industry/CFM/Flash Card.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D09F8A7-0EAA-4DBD-AB5C-6B7B14F6DB22}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D05C1C0C-7335-4B6F-94F1-C2A6A92A50E4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12780" yWindow="2160" windowWidth="21285" windowHeight="16680" firstSheet="4" activeTab="8" xr2:uid="{9A28822D-BA55-F242-829D-3FA5BE3F147C}"/>
+    <workbookView xWindow="12780" yWindow="2160" windowWidth="21285" windowHeight="16680" xr2:uid="{9A28822D-BA55-F242-829D-3FA5BE3F147C}"/>
   </bookViews>
   <sheets>
     <sheet name="MicroSD 16GB(Channel)" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1023" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1248" uniqueCount="9">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="0" type="noConversion"/>
@@ -507,7 +507,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B272F1F1-C221-BA47-B841-D5FD2627A973}">
-  <dimension ref="A1:H125"/>
+  <dimension ref="A1:H150"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.6640625" style="8" bestFit="1" customWidth="1"/>
@@ -3517,6 +3517,581 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A126" s="8">
+        <v>46050</v>
+      </c>
+      <c r="B126" s="8">
+        <v>46050</v>
+      </c>
+      <c r="C126" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D126" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E126" s="11">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F126" s="11">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="G126" s="11">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A127" s="8">
+        <v>46051</v>
+      </c>
+      <c r="B127" s="8">
+        <v>46051</v>
+      </c>
+      <c r="C127" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D127" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E127" s="11">
+        <v>2.4</v>
+      </c>
+      <c r="F127" s="11">
+        <v>2.4</v>
+      </c>
+      <c r="G127" s="11">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A128" s="8">
+        <v>46052</v>
+      </c>
+      <c r="B128" s="8">
+        <v>46052</v>
+      </c>
+      <c r="C128" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D128" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E128" s="11">
+        <v>2.4</v>
+      </c>
+      <c r="F128" s="11">
+        <v>2.4</v>
+      </c>
+      <c r="G128" s="11">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A129" s="8">
+        <v>46055</v>
+      </c>
+      <c r="B129" s="8">
+        <v>46055</v>
+      </c>
+      <c r="C129" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D129" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E129" s="11">
+        <v>2.4</v>
+      </c>
+      <c r="F129" s="11">
+        <v>2.4</v>
+      </c>
+      <c r="G129" s="11">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A130" s="8">
+        <v>46056</v>
+      </c>
+      <c r="B130" s="8">
+        <v>46056</v>
+      </c>
+      <c r="C130" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D130" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E130" s="11">
+        <v>2.4</v>
+      </c>
+      <c r="F130" s="11">
+        <v>2.4</v>
+      </c>
+      <c r="G130" s="11">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A131" s="8">
+        <v>46057</v>
+      </c>
+      <c r="B131" s="8">
+        <v>46057</v>
+      </c>
+      <c r="C131" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D131" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E131" s="11">
+        <v>2.4</v>
+      </c>
+      <c r="F131" s="11">
+        <v>2.4</v>
+      </c>
+      <c r="G131" s="11">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A132" s="8">
+        <v>46058</v>
+      </c>
+      <c r="B132" s="8">
+        <v>46058</v>
+      </c>
+      <c r="C132" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D132" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E132" s="11">
+        <v>2.4</v>
+      </c>
+      <c r="F132" s="11">
+        <v>2.4</v>
+      </c>
+      <c r="G132" s="11">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A133" s="8">
+        <v>46059</v>
+      </c>
+      <c r="B133" s="8">
+        <v>46059</v>
+      </c>
+      <c r="C133" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D133" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E133" s="11">
+        <v>2.4</v>
+      </c>
+      <c r="F133" s="11">
+        <v>2.4</v>
+      </c>
+      <c r="G133" s="11">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A134" s="8">
+        <v>46062</v>
+      </c>
+      <c r="B134" s="8">
+        <v>46062</v>
+      </c>
+      <c r="C134" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D134" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E134" s="11">
+        <v>2.5</v>
+      </c>
+      <c r="F134" s="11">
+        <v>2.5</v>
+      </c>
+      <c r="G134" s="11">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A135" s="8">
+        <v>46063</v>
+      </c>
+      <c r="B135" s="8">
+        <v>46063</v>
+      </c>
+      <c r="C135" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D135" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E135" s="11">
+        <v>2.5</v>
+      </c>
+      <c r="F135" s="11">
+        <v>2.5</v>
+      </c>
+      <c r="G135" s="11">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A136" s="8">
+        <v>46064</v>
+      </c>
+      <c r="B136" s="8">
+        <v>46064</v>
+      </c>
+      <c r="C136" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D136" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E136" s="11">
+        <v>2.5</v>
+      </c>
+      <c r="F136" s="11">
+        <v>2.5</v>
+      </c>
+      <c r="G136" s="11">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A137" s="8">
+        <v>46065</v>
+      </c>
+      <c r="B137" s="8">
+        <v>46065</v>
+      </c>
+      <c r="C137" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D137" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E137" s="11">
+        <v>2.5</v>
+      </c>
+      <c r="F137" s="11">
+        <v>2.5</v>
+      </c>
+      <c r="G137" s="11">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A138" s="8">
+        <v>46066</v>
+      </c>
+      <c r="B138" s="8">
+        <v>46066</v>
+      </c>
+      <c r="C138" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D138" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E138" s="11">
+        <v>2.5</v>
+      </c>
+      <c r="F138" s="11">
+        <v>2.5</v>
+      </c>
+      <c r="G138" s="11">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A139" s="8">
+        <v>46067</v>
+      </c>
+      <c r="B139" s="8">
+        <v>46067</v>
+      </c>
+      <c r="C139" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D139" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E139" s="11">
+        <v>2.5</v>
+      </c>
+      <c r="F139" s="11">
+        <v>2.5</v>
+      </c>
+      <c r="G139" s="11">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A140" s="8">
+        <v>46077</v>
+      </c>
+      <c r="B140" s="8">
+        <v>46077</v>
+      </c>
+      <c r="C140" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D140" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E140" s="11">
+        <v>2.5</v>
+      </c>
+      <c r="F140" s="11">
+        <v>2.5</v>
+      </c>
+      <c r="G140" s="11">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A141" s="8">
+        <v>46078</v>
+      </c>
+      <c r="B141" s="8">
+        <v>46078</v>
+      </c>
+      <c r="C141" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D141" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E141" s="11">
+        <v>2.5</v>
+      </c>
+      <c r="F141" s="11">
+        <v>2.5</v>
+      </c>
+      <c r="G141" s="11">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A142" s="8">
+        <v>46079</v>
+      </c>
+      <c r="B142" s="8">
+        <v>46079</v>
+      </c>
+      <c r="C142" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D142" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E142" s="11">
+        <v>2.5</v>
+      </c>
+      <c r="F142" s="11">
+        <v>2.5</v>
+      </c>
+      <c r="G142" s="11">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A143" s="8">
+        <v>46080</v>
+      </c>
+      <c r="B143" s="8">
+        <v>46080</v>
+      </c>
+      <c r="C143" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D143" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E143" s="11">
+        <v>2.5</v>
+      </c>
+      <c r="F143" s="11">
+        <v>2.5</v>
+      </c>
+      <c r="G143" s="11">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A144" s="8">
+        <v>46083</v>
+      </c>
+      <c r="B144" s="8">
+        <v>46083</v>
+      </c>
+      <c r="C144" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D144" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E144" s="11">
+        <v>2.5</v>
+      </c>
+      <c r="F144" s="11">
+        <v>2.5</v>
+      </c>
+      <c r="G144" s="11">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A145" s="8">
+        <v>46084</v>
+      </c>
+      <c r="B145" s="8">
+        <v>46084</v>
+      </c>
+      <c r="C145" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D145" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E145" s="11">
+        <v>2.5</v>
+      </c>
+      <c r="F145" s="11">
+        <v>2.5</v>
+      </c>
+      <c r="G145" s="11">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A146" s="8">
+        <v>46085</v>
+      </c>
+      <c r="B146" s="8">
+        <v>46085</v>
+      </c>
+      <c r="C146" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D146" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E146" s="11">
+        <v>2.5</v>
+      </c>
+      <c r="F146" s="11">
+        <v>2.5</v>
+      </c>
+      <c r="G146" s="11">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A147" s="8">
+        <v>46086</v>
+      </c>
+      <c r="B147" s="8">
+        <v>46086</v>
+      </c>
+      <c r="C147" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D147" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E147" s="11">
+        <v>2.5</v>
+      </c>
+      <c r="F147" s="11">
+        <v>2.5</v>
+      </c>
+      <c r="G147" s="11">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A148" s="8">
+        <v>46087</v>
+      </c>
+      <c r="B148" s="8">
+        <v>46087</v>
+      </c>
+      <c r="C148" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D148" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E148" s="11">
+        <v>2.9</v>
+      </c>
+      <c r="F148" s="11">
+        <v>2.9</v>
+      </c>
+      <c r="G148" s="11">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A149" s="8">
+        <v>46090</v>
+      </c>
+      <c r="B149" s="8">
+        <v>46090</v>
+      </c>
+      <c r="C149" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D149" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E149" s="11">
+        <v>2.9</v>
+      </c>
+      <c r="F149" s="11">
+        <v>2.9</v>
+      </c>
+      <c r="G149" s="11">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A150" s="8">
+        <v>46091</v>
+      </c>
+      <c r="B150" s="8">
+        <v>46091</v>
+      </c>
+      <c r="C150" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D150" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E150" s="11">
+        <v>2.9</v>
+      </c>
+      <c r="F150" s="11">
+        <v>2.9</v>
+      </c>
+      <c r="G150" s="11">
+        <v>2.9</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3525,7 +4100,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EA8D367-2C3B-E14E-A57E-CFD56EE7448B}">
-  <dimension ref="A1:H125"/>
+  <dimension ref="A1:H150"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.6640625" style="8" bestFit="1" customWidth="1"/>
@@ -6535,6 +7110,581 @@
         <v>4.5</v>
       </c>
     </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A126" s="8">
+        <v>46050</v>
+      </c>
+      <c r="B126" s="8">
+        <v>46050</v>
+      </c>
+      <c r="C126" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D126" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E126" s="11">
+        <v>4.5</v>
+      </c>
+      <c r="F126" s="11">
+        <v>4.5</v>
+      </c>
+      <c r="G126" s="11">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A127" s="8">
+        <v>46051</v>
+      </c>
+      <c r="B127" s="8">
+        <v>46051</v>
+      </c>
+      <c r="C127" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D127" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E127" s="11">
+        <v>4.7</v>
+      </c>
+      <c r="F127" s="11">
+        <v>4.7</v>
+      </c>
+      <c r="G127" s="11">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A128" s="8">
+        <v>46052</v>
+      </c>
+      <c r="B128" s="8">
+        <v>46052</v>
+      </c>
+      <c r="C128" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D128" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E128" s="11">
+        <v>4.7</v>
+      </c>
+      <c r="F128" s="11">
+        <v>4.7</v>
+      </c>
+      <c r="G128" s="11">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A129" s="8">
+        <v>46055</v>
+      </c>
+      <c r="B129" s="8">
+        <v>46055</v>
+      </c>
+      <c r="C129" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D129" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E129" s="11">
+        <v>4.7</v>
+      </c>
+      <c r="F129" s="11">
+        <v>4.7</v>
+      </c>
+      <c r="G129" s="11">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A130" s="8">
+        <v>46056</v>
+      </c>
+      <c r="B130" s="8">
+        <v>46056</v>
+      </c>
+      <c r="C130" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D130" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E130" s="11">
+        <v>4.7</v>
+      </c>
+      <c r="F130" s="11">
+        <v>4.7</v>
+      </c>
+      <c r="G130" s="11">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A131" s="8">
+        <v>46057</v>
+      </c>
+      <c r="B131" s="8">
+        <v>46057</v>
+      </c>
+      <c r="C131" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D131" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E131" s="11">
+        <v>4.7</v>
+      </c>
+      <c r="F131" s="11">
+        <v>4.7</v>
+      </c>
+      <c r="G131" s="11">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A132" s="8">
+        <v>46058</v>
+      </c>
+      <c r="B132" s="8">
+        <v>46058</v>
+      </c>
+      <c r="C132" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D132" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E132" s="11">
+        <v>4.7</v>
+      </c>
+      <c r="F132" s="11">
+        <v>4.7</v>
+      </c>
+      <c r="G132" s="11">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A133" s="8">
+        <v>46059</v>
+      </c>
+      <c r="B133" s="8">
+        <v>46059</v>
+      </c>
+      <c r="C133" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D133" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E133" s="11">
+        <v>4.7</v>
+      </c>
+      <c r="F133" s="11">
+        <v>4.7</v>
+      </c>
+      <c r="G133" s="11">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A134" s="8">
+        <v>46062</v>
+      </c>
+      <c r="B134" s="8">
+        <v>46062</v>
+      </c>
+      <c r="C134" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D134" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E134" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="F134" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="G134" s="11">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A135" s="8">
+        <v>46063</v>
+      </c>
+      <c r="B135" s="8">
+        <v>46063</v>
+      </c>
+      <c r="C135" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D135" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E135" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="F135" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="G135" s="11">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A136" s="8">
+        <v>46064</v>
+      </c>
+      <c r="B136" s="8">
+        <v>46064</v>
+      </c>
+      <c r="C136" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D136" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E136" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="F136" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="G136" s="11">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A137" s="8">
+        <v>46065</v>
+      </c>
+      <c r="B137" s="8">
+        <v>46065</v>
+      </c>
+      <c r="C137" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D137" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E137" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="F137" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="G137" s="11">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A138" s="8">
+        <v>46066</v>
+      </c>
+      <c r="B138" s="8">
+        <v>46066</v>
+      </c>
+      <c r="C138" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D138" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E138" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="F138" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="G138" s="11">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A139" s="8">
+        <v>46067</v>
+      </c>
+      <c r="B139" s="8">
+        <v>46067</v>
+      </c>
+      <c r="C139" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D139" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E139" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="F139" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="G139" s="11">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A140" s="8">
+        <v>46077</v>
+      </c>
+      <c r="B140" s="8">
+        <v>46077</v>
+      </c>
+      <c r="C140" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D140" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E140" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="F140" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="G140" s="11">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A141" s="8">
+        <v>46078</v>
+      </c>
+      <c r="B141" s="8">
+        <v>46078</v>
+      </c>
+      <c r="C141" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D141" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E141" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="F141" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="G141" s="11">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A142" s="8">
+        <v>46079</v>
+      </c>
+      <c r="B142" s="8">
+        <v>46079</v>
+      </c>
+      <c r="C142" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D142" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E142" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="F142" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="G142" s="11">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A143" s="8">
+        <v>46080</v>
+      </c>
+      <c r="B143" s="8">
+        <v>46080</v>
+      </c>
+      <c r="C143" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D143" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E143" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="F143" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="G143" s="11">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A144" s="8">
+        <v>46083</v>
+      </c>
+      <c r="B144" s="8">
+        <v>46083</v>
+      </c>
+      <c r="C144" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D144" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E144" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="F144" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="G144" s="11">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A145" s="8">
+        <v>46084</v>
+      </c>
+      <c r="B145" s="8">
+        <v>46084</v>
+      </c>
+      <c r="C145" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D145" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E145" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="F145" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="G145" s="11">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A146" s="8">
+        <v>46085</v>
+      </c>
+      <c r="B146" s="8">
+        <v>46085</v>
+      </c>
+      <c r="C146" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D146" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E146" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="F146" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="G146" s="11">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A147" s="8">
+        <v>46086</v>
+      </c>
+      <c r="B147" s="8">
+        <v>46086</v>
+      </c>
+      <c r="C147" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D147" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E147" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="F147" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="G147" s="11">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A148" s="8">
+        <v>46087</v>
+      </c>
+      <c r="B148" s="8">
+        <v>46087</v>
+      </c>
+      <c r="C148" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D148" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E148" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="F148" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="G148" s="11">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A149" s="8">
+        <v>46090</v>
+      </c>
+      <c r="B149" s="8">
+        <v>46090</v>
+      </c>
+      <c r="C149" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D149" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E149" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="F149" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="G149" s="11">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A150" s="8">
+        <v>46091</v>
+      </c>
+      <c r="B150" s="8">
+        <v>46091</v>
+      </c>
+      <c r="C150" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D150" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E150" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="F150" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="G150" s="11">
+        <v>5.5</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6543,7 +7693,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDA7DDA5-51A1-B549-8D1A-904152A54486}">
-  <dimension ref="A1:H125"/>
+  <dimension ref="A1:H150"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.6640625" style="8" bestFit="1" customWidth="1"/>
@@ -9553,6 +10703,581 @@
         <v>6</v>
       </c>
     </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A126" s="8">
+        <v>46050</v>
+      </c>
+      <c r="B126" s="8">
+        <v>46050</v>
+      </c>
+      <c r="C126" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D126" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E126" s="11">
+        <v>6</v>
+      </c>
+      <c r="F126" s="11">
+        <v>6</v>
+      </c>
+      <c r="G126" s="11">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A127" s="8">
+        <v>46051</v>
+      </c>
+      <c r="B127" s="8">
+        <v>46051</v>
+      </c>
+      <c r="C127" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D127" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E127" s="11">
+        <v>6.5</v>
+      </c>
+      <c r="F127" s="11">
+        <v>6.5</v>
+      </c>
+      <c r="G127" s="11">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A128" s="8">
+        <v>46052</v>
+      </c>
+      <c r="B128" s="8">
+        <v>46052</v>
+      </c>
+      <c r="C128" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D128" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E128" s="11">
+        <v>6.5</v>
+      </c>
+      <c r="F128" s="11">
+        <v>6.5</v>
+      </c>
+      <c r="G128" s="11">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A129" s="8">
+        <v>46055</v>
+      </c>
+      <c r="B129" s="8">
+        <v>46055</v>
+      </c>
+      <c r="C129" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D129" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E129" s="11">
+        <v>6.5</v>
+      </c>
+      <c r="F129" s="11">
+        <v>6.5</v>
+      </c>
+      <c r="G129" s="11">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A130" s="8">
+        <v>46056</v>
+      </c>
+      <c r="B130" s="8">
+        <v>46056</v>
+      </c>
+      <c r="C130" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D130" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E130" s="11">
+        <v>6.5</v>
+      </c>
+      <c r="F130" s="11">
+        <v>6.5</v>
+      </c>
+      <c r="G130" s="11">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A131" s="8">
+        <v>46057</v>
+      </c>
+      <c r="B131" s="8">
+        <v>46057</v>
+      </c>
+      <c r="C131" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D131" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E131" s="11">
+        <v>6.5</v>
+      </c>
+      <c r="F131" s="11">
+        <v>6.5</v>
+      </c>
+      <c r="G131" s="11">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A132" s="8">
+        <v>46058</v>
+      </c>
+      <c r="B132" s="8">
+        <v>46058</v>
+      </c>
+      <c r="C132" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D132" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E132" s="11">
+        <v>6.5</v>
+      </c>
+      <c r="F132" s="11">
+        <v>6.5</v>
+      </c>
+      <c r="G132" s="11">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A133" s="8">
+        <v>46059</v>
+      </c>
+      <c r="B133" s="8">
+        <v>46059</v>
+      </c>
+      <c r="C133" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D133" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E133" s="11">
+        <v>6.5</v>
+      </c>
+      <c r="F133" s="11">
+        <v>6.5</v>
+      </c>
+      <c r="G133" s="11">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A134" s="8">
+        <v>46062</v>
+      </c>
+      <c r="B134" s="8">
+        <v>46062</v>
+      </c>
+      <c r="C134" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D134" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E134" s="11">
+        <v>6.7</v>
+      </c>
+      <c r="F134" s="11">
+        <v>6.7</v>
+      </c>
+      <c r="G134" s="11">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A135" s="8">
+        <v>46063</v>
+      </c>
+      <c r="B135" s="8">
+        <v>46063</v>
+      </c>
+      <c r="C135" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D135" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E135" s="11">
+        <v>6.7</v>
+      </c>
+      <c r="F135" s="11">
+        <v>6.7</v>
+      </c>
+      <c r="G135" s="11">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A136" s="8">
+        <v>46064</v>
+      </c>
+      <c r="B136" s="8">
+        <v>46064</v>
+      </c>
+      <c r="C136" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D136" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E136" s="11">
+        <v>6.7</v>
+      </c>
+      <c r="F136" s="11">
+        <v>6.7</v>
+      </c>
+      <c r="G136" s="11">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A137" s="8">
+        <v>46065</v>
+      </c>
+      <c r="B137" s="8">
+        <v>46065</v>
+      </c>
+      <c r="C137" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D137" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E137" s="11">
+        <v>6.7</v>
+      </c>
+      <c r="F137" s="11">
+        <v>6.7</v>
+      </c>
+      <c r="G137" s="11">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A138" s="8">
+        <v>46066</v>
+      </c>
+      <c r="B138" s="8">
+        <v>46066</v>
+      </c>
+      <c r="C138" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D138" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E138" s="11">
+        <v>6.7</v>
+      </c>
+      <c r="F138" s="11">
+        <v>6.7</v>
+      </c>
+      <c r="G138" s="11">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A139" s="8">
+        <v>46067</v>
+      </c>
+      <c r="B139" s="8">
+        <v>46067</v>
+      </c>
+      <c r="C139" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D139" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E139" s="11">
+        <v>6.7</v>
+      </c>
+      <c r="F139" s="11">
+        <v>6.7</v>
+      </c>
+      <c r="G139" s="11">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A140" s="8">
+        <v>46077</v>
+      </c>
+      <c r="B140" s="8">
+        <v>46077</v>
+      </c>
+      <c r="C140" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D140" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E140" s="11">
+        <v>6.7</v>
+      </c>
+      <c r="F140" s="11">
+        <v>6.7</v>
+      </c>
+      <c r="G140" s="11">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A141" s="8">
+        <v>46078</v>
+      </c>
+      <c r="B141" s="8">
+        <v>46078</v>
+      </c>
+      <c r="C141" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D141" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E141" s="11">
+        <v>6.7</v>
+      </c>
+      <c r="F141" s="11">
+        <v>6.7</v>
+      </c>
+      <c r="G141" s="11">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A142" s="8">
+        <v>46079</v>
+      </c>
+      <c r="B142" s="8">
+        <v>46079</v>
+      </c>
+      <c r="C142" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D142" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E142" s="11">
+        <v>6.7</v>
+      </c>
+      <c r="F142" s="11">
+        <v>6.7</v>
+      </c>
+      <c r="G142" s="11">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A143" s="8">
+        <v>46080</v>
+      </c>
+      <c r="B143" s="8">
+        <v>46080</v>
+      </c>
+      <c r="C143" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D143" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E143" s="11">
+        <v>6.7</v>
+      </c>
+      <c r="F143" s="11">
+        <v>6.7</v>
+      </c>
+      <c r="G143" s="11">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A144" s="8">
+        <v>46083</v>
+      </c>
+      <c r="B144" s="8">
+        <v>46083</v>
+      </c>
+      <c r="C144" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D144" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E144" s="11">
+        <v>6.7</v>
+      </c>
+      <c r="F144" s="11">
+        <v>6.7</v>
+      </c>
+      <c r="G144" s="11">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A145" s="8">
+        <v>46084</v>
+      </c>
+      <c r="B145" s="8">
+        <v>46084</v>
+      </c>
+      <c r="C145" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D145" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E145" s="11">
+        <v>6.7</v>
+      </c>
+      <c r="F145" s="11">
+        <v>6.7</v>
+      </c>
+      <c r="G145" s="11">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A146" s="8">
+        <v>46085</v>
+      </c>
+      <c r="B146" s="8">
+        <v>46085</v>
+      </c>
+      <c r="C146" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D146" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E146" s="11">
+        <v>6.7</v>
+      </c>
+      <c r="F146" s="11">
+        <v>6.7</v>
+      </c>
+      <c r="G146" s="11">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A147" s="8">
+        <v>46086</v>
+      </c>
+      <c r="B147" s="8">
+        <v>46086</v>
+      </c>
+      <c r="C147" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D147" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E147" s="11">
+        <v>6.7</v>
+      </c>
+      <c r="F147" s="11">
+        <v>6.7</v>
+      </c>
+      <c r="G147" s="11">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A148" s="8">
+        <v>46087</v>
+      </c>
+      <c r="B148" s="8">
+        <v>46087</v>
+      </c>
+      <c r="C148" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D148" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E148" s="11">
+        <v>7.5</v>
+      </c>
+      <c r="F148" s="11">
+        <v>7.5</v>
+      </c>
+      <c r="G148" s="11">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A149" s="8">
+        <v>46090</v>
+      </c>
+      <c r="B149" s="8">
+        <v>46090</v>
+      </c>
+      <c r="C149" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D149" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E149" s="11">
+        <v>8</v>
+      </c>
+      <c r="F149" s="11">
+        <v>8</v>
+      </c>
+      <c r="G149" s="11">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A150" s="8">
+        <v>46091</v>
+      </c>
+      <c r="B150" s="8">
+        <v>46091</v>
+      </c>
+      <c r="C150" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D150" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E150" s="11">
+        <v>8</v>
+      </c>
+      <c r="F150" s="11">
+        <v>8</v>
+      </c>
+      <c r="G150" s="11">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9561,7 +11286,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0DFD583-C049-7E44-B4FF-4B3CC56372E6}">
-  <dimension ref="A1:H125"/>
+  <dimension ref="A1:H150"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.6640625" style="8" bestFit="1" customWidth="1"/>
@@ -12571,6 +14296,581 @@
         <v>12</v>
       </c>
     </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A126" s="8">
+        <v>46050</v>
+      </c>
+      <c r="B126" s="8">
+        <v>46050</v>
+      </c>
+      <c r="C126" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D126" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E126" s="11">
+        <v>12</v>
+      </c>
+      <c r="F126" s="11">
+        <v>12</v>
+      </c>
+      <c r="G126" s="11">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A127" s="8">
+        <v>46051</v>
+      </c>
+      <c r="B127" s="8">
+        <v>46051</v>
+      </c>
+      <c r="C127" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D127" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E127" s="11">
+        <v>13</v>
+      </c>
+      <c r="F127" s="11">
+        <v>13</v>
+      </c>
+      <c r="G127" s="11">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A128" s="8">
+        <v>46052</v>
+      </c>
+      <c r="B128" s="8">
+        <v>46052</v>
+      </c>
+      <c r="C128" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D128" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E128" s="11">
+        <v>13</v>
+      </c>
+      <c r="F128" s="11">
+        <v>13</v>
+      </c>
+      <c r="G128" s="11">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A129" s="8">
+        <v>46055</v>
+      </c>
+      <c r="B129" s="8">
+        <v>46055</v>
+      </c>
+      <c r="C129" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D129" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E129" s="11">
+        <v>13</v>
+      </c>
+      <c r="F129" s="11">
+        <v>13</v>
+      </c>
+      <c r="G129" s="11">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A130" s="8">
+        <v>46056</v>
+      </c>
+      <c r="B130" s="8">
+        <v>46056</v>
+      </c>
+      <c r="C130" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D130" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E130" s="11">
+        <v>13</v>
+      </c>
+      <c r="F130" s="11">
+        <v>13</v>
+      </c>
+      <c r="G130" s="11">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A131" s="8">
+        <v>46057</v>
+      </c>
+      <c r="B131" s="8">
+        <v>46057</v>
+      </c>
+      <c r="C131" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D131" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E131" s="11">
+        <v>13</v>
+      </c>
+      <c r="F131" s="11">
+        <v>13</v>
+      </c>
+      <c r="G131" s="11">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A132" s="8">
+        <v>46058</v>
+      </c>
+      <c r="B132" s="8">
+        <v>46058</v>
+      </c>
+      <c r="C132" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D132" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E132" s="11">
+        <v>13</v>
+      </c>
+      <c r="F132" s="11">
+        <v>13</v>
+      </c>
+      <c r="G132" s="11">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A133" s="8">
+        <v>46059</v>
+      </c>
+      <c r="B133" s="8">
+        <v>46059</v>
+      </c>
+      <c r="C133" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D133" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E133" s="11">
+        <v>13</v>
+      </c>
+      <c r="F133" s="11">
+        <v>13</v>
+      </c>
+      <c r="G133" s="11">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A134" s="8">
+        <v>46062</v>
+      </c>
+      <c r="B134" s="8">
+        <v>46062</v>
+      </c>
+      <c r="C134" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D134" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E134" s="11">
+        <v>13</v>
+      </c>
+      <c r="F134" s="11">
+        <v>13</v>
+      </c>
+      <c r="G134" s="11">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A135" s="8">
+        <v>46063</v>
+      </c>
+      <c r="B135" s="8">
+        <v>46063</v>
+      </c>
+      <c r="C135" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D135" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E135" s="11">
+        <v>13</v>
+      </c>
+      <c r="F135" s="11">
+        <v>13</v>
+      </c>
+      <c r="G135" s="11">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A136" s="8">
+        <v>46064</v>
+      </c>
+      <c r="B136" s="8">
+        <v>46064</v>
+      </c>
+      <c r="C136" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D136" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E136" s="11">
+        <v>13</v>
+      </c>
+      <c r="F136" s="11">
+        <v>13</v>
+      </c>
+      <c r="G136" s="11">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A137" s="8">
+        <v>46065</v>
+      </c>
+      <c r="B137" s="8">
+        <v>46065</v>
+      </c>
+      <c r="C137" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D137" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E137" s="11">
+        <v>13</v>
+      </c>
+      <c r="F137" s="11">
+        <v>13</v>
+      </c>
+      <c r="G137" s="11">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A138" s="8">
+        <v>46066</v>
+      </c>
+      <c r="B138" s="8">
+        <v>46066</v>
+      </c>
+      <c r="C138" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D138" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E138" s="11">
+        <v>13</v>
+      </c>
+      <c r="F138" s="11">
+        <v>13</v>
+      </c>
+      <c r="G138" s="11">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A139" s="8">
+        <v>46067</v>
+      </c>
+      <c r="B139" s="8">
+        <v>46067</v>
+      </c>
+      <c r="C139" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D139" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E139" s="11">
+        <v>13</v>
+      </c>
+      <c r="F139" s="11">
+        <v>13</v>
+      </c>
+      <c r="G139" s="11">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A140" s="8">
+        <v>46077</v>
+      </c>
+      <c r="B140" s="8">
+        <v>46077</v>
+      </c>
+      <c r="C140" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D140" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E140" s="11">
+        <v>13</v>
+      </c>
+      <c r="F140" s="11">
+        <v>13</v>
+      </c>
+      <c r="G140" s="11">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A141" s="8">
+        <v>46078</v>
+      </c>
+      <c r="B141" s="8">
+        <v>46078</v>
+      </c>
+      <c r="C141" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D141" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E141" s="11">
+        <v>13</v>
+      </c>
+      <c r="F141" s="11">
+        <v>13</v>
+      </c>
+      <c r="G141" s="11">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A142" s="8">
+        <v>46079</v>
+      </c>
+      <c r="B142" s="8">
+        <v>46079</v>
+      </c>
+      <c r="C142" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D142" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E142" s="11">
+        <v>13</v>
+      </c>
+      <c r="F142" s="11">
+        <v>13</v>
+      </c>
+      <c r="G142" s="11">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A143" s="8">
+        <v>46080</v>
+      </c>
+      <c r="B143" s="8">
+        <v>46080</v>
+      </c>
+      <c r="C143" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D143" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E143" s="11">
+        <v>13</v>
+      </c>
+      <c r="F143" s="11">
+        <v>13</v>
+      </c>
+      <c r="G143" s="11">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A144" s="8">
+        <v>46083</v>
+      </c>
+      <c r="B144" s="8">
+        <v>46083</v>
+      </c>
+      <c r="C144" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D144" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E144" s="11">
+        <v>13</v>
+      </c>
+      <c r="F144" s="11">
+        <v>13</v>
+      </c>
+      <c r="G144" s="11">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A145" s="8">
+        <v>46084</v>
+      </c>
+      <c r="B145" s="8">
+        <v>46084</v>
+      </c>
+      <c r="C145" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D145" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E145" s="11">
+        <v>13</v>
+      </c>
+      <c r="F145" s="11">
+        <v>13</v>
+      </c>
+      <c r="G145" s="11">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A146" s="8">
+        <v>46085</v>
+      </c>
+      <c r="B146" s="8">
+        <v>46085</v>
+      </c>
+      <c r="C146" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D146" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E146" s="11">
+        <v>13</v>
+      </c>
+      <c r="F146" s="11">
+        <v>13</v>
+      </c>
+      <c r="G146" s="11">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A147" s="8">
+        <v>46086</v>
+      </c>
+      <c r="B147" s="8">
+        <v>46086</v>
+      </c>
+      <c r="C147" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D147" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E147" s="11">
+        <v>13</v>
+      </c>
+      <c r="F147" s="11">
+        <v>13</v>
+      </c>
+      <c r="G147" s="11">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A148" s="8">
+        <v>46087</v>
+      </c>
+      <c r="B148" s="8">
+        <v>46087</v>
+      </c>
+      <c r="C148" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D148" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E148" s="11">
+        <v>14.5</v>
+      </c>
+      <c r="F148" s="11">
+        <v>14.5</v>
+      </c>
+      <c r="G148" s="11">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A149" s="8">
+        <v>46090</v>
+      </c>
+      <c r="B149" s="8">
+        <v>46090</v>
+      </c>
+      <c r="C149" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D149" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E149" s="11">
+        <v>16</v>
+      </c>
+      <c r="F149" s="11">
+        <v>16</v>
+      </c>
+      <c r="G149" s="11">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A150" s="8">
+        <v>46091</v>
+      </c>
+      <c r="B150" s="8">
+        <v>46091</v>
+      </c>
+      <c r="C150" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D150" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E150" s="11">
+        <v>16</v>
+      </c>
+      <c r="F150" s="11">
+        <v>16</v>
+      </c>
+      <c r="G150" s="11">
+        <v>16</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12579,7 +14879,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3239D1C2-C3DC-9D47-B02E-5855318CF9C1}">
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:H72"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.6640625" style="8" bestFit="1" customWidth="1"/>
@@ -13717,6 +16017,581 @@
         <v>37</v>
       </c>
     </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A48" s="8">
+        <v>46050</v>
+      </c>
+      <c r="B48" s="8">
+        <v>46050</v>
+      </c>
+      <c r="C48" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="11">
+        <v>37</v>
+      </c>
+      <c r="F48" s="11">
+        <v>37</v>
+      </c>
+      <c r="G48" s="11">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A49" s="8">
+        <v>46051</v>
+      </c>
+      <c r="B49" s="8">
+        <v>46051</v>
+      </c>
+      <c r="C49" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="11">
+        <v>37</v>
+      </c>
+      <c r="F49" s="11">
+        <v>37</v>
+      </c>
+      <c r="G49" s="11">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A50" s="8">
+        <v>46052</v>
+      </c>
+      <c r="B50" s="8">
+        <v>46052</v>
+      </c>
+      <c r="C50" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="11">
+        <v>37</v>
+      </c>
+      <c r="F50" s="11">
+        <v>37</v>
+      </c>
+      <c r="G50" s="11">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A51" s="8">
+        <v>46055</v>
+      </c>
+      <c r="B51" s="8">
+        <v>46055</v>
+      </c>
+      <c r="C51" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" s="11">
+        <v>37</v>
+      </c>
+      <c r="F51" s="11">
+        <v>37</v>
+      </c>
+      <c r="G51" s="11">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A52" s="8">
+        <v>46056</v>
+      </c>
+      <c r="B52" s="8">
+        <v>46056</v>
+      </c>
+      <c r="C52" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="11">
+        <v>37</v>
+      </c>
+      <c r="F52" s="11">
+        <v>37</v>
+      </c>
+      <c r="G52" s="11">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A53" s="8">
+        <v>46057</v>
+      </c>
+      <c r="B53" s="8">
+        <v>46057</v>
+      </c>
+      <c r="C53" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E53" s="11">
+        <v>37</v>
+      </c>
+      <c r="F53" s="11">
+        <v>37</v>
+      </c>
+      <c r="G53" s="11">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="8">
+        <v>46058</v>
+      </c>
+      <c r="B54" s="8">
+        <v>46058</v>
+      </c>
+      <c r="C54" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="11">
+        <v>37</v>
+      </c>
+      <c r="F54" s="11">
+        <v>37</v>
+      </c>
+      <c r="G54" s="11">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="8">
+        <v>46059</v>
+      </c>
+      <c r="B55" s="8">
+        <v>46059</v>
+      </c>
+      <c r="C55" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="11">
+        <v>37</v>
+      </c>
+      <c r="F55" s="11">
+        <v>37</v>
+      </c>
+      <c r="G55" s="11">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="8">
+        <v>46062</v>
+      </c>
+      <c r="B56" s="8">
+        <v>46062</v>
+      </c>
+      <c r="C56" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="11">
+        <v>37</v>
+      </c>
+      <c r="F56" s="11">
+        <v>37</v>
+      </c>
+      <c r="G56" s="11">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="8">
+        <v>46063</v>
+      </c>
+      <c r="B57" s="8">
+        <v>46063</v>
+      </c>
+      <c r="C57" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="11">
+        <v>37</v>
+      </c>
+      <c r="F57" s="11">
+        <v>37</v>
+      </c>
+      <c r="G57" s="11">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="8">
+        <v>46064</v>
+      </c>
+      <c r="B58" s="8">
+        <v>46064</v>
+      </c>
+      <c r="C58" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="11">
+        <v>37</v>
+      </c>
+      <c r="F58" s="11">
+        <v>37</v>
+      </c>
+      <c r="G58" s="11">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="8">
+        <v>46065</v>
+      </c>
+      <c r="B59" s="8">
+        <v>46065</v>
+      </c>
+      <c r="C59" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="11">
+        <v>37</v>
+      </c>
+      <c r="F59" s="11">
+        <v>37</v>
+      </c>
+      <c r="G59" s="11">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="8">
+        <v>46066</v>
+      </c>
+      <c r="B60" s="8">
+        <v>46066</v>
+      </c>
+      <c r="C60" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D60" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="11">
+        <v>37</v>
+      </c>
+      <c r="F60" s="11">
+        <v>37</v>
+      </c>
+      <c r="G60" s="11">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A61" s="8">
+        <v>46067</v>
+      </c>
+      <c r="B61" s="8">
+        <v>46067</v>
+      </c>
+      <c r="C61" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D61" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E61" s="11">
+        <v>37</v>
+      </c>
+      <c r="F61" s="11">
+        <v>37</v>
+      </c>
+      <c r="G61" s="11">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A62" s="8">
+        <v>46077</v>
+      </c>
+      <c r="B62" s="8">
+        <v>46077</v>
+      </c>
+      <c r="C62" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D62" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E62" s="11">
+        <v>37</v>
+      </c>
+      <c r="F62" s="11">
+        <v>37</v>
+      </c>
+      <c r="G62" s="11">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A63" s="8">
+        <v>46078</v>
+      </c>
+      <c r="B63" s="8">
+        <v>46078</v>
+      </c>
+      <c r="C63" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D63" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E63" s="11">
+        <v>37</v>
+      </c>
+      <c r="F63" s="11">
+        <v>37</v>
+      </c>
+      <c r="G63" s="11">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A64" s="8">
+        <v>46079</v>
+      </c>
+      <c r="B64" s="8">
+        <v>46079</v>
+      </c>
+      <c r="C64" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D64" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E64" s="11">
+        <v>37</v>
+      </c>
+      <c r="F64" s="11">
+        <v>37</v>
+      </c>
+      <c r="G64" s="11">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A65" s="8">
+        <v>46080</v>
+      </c>
+      <c r="B65" s="8">
+        <v>46080</v>
+      </c>
+      <c r="C65" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D65" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E65" s="11">
+        <v>37</v>
+      </c>
+      <c r="F65" s="11">
+        <v>37</v>
+      </c>
+      <c r="G65" s="11">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A66" s="8">
+        <v>46083</v>
+      </c>
+      <c r="B66" s="8">
+        <v>46083</v>
+      </c>
+      <c r="C66" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D66" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E66" s="11">
+        <v>37</v>
+      </c>
+      <c r="F66" s="11">
+        <v>37</v>
+      </c>
+      <c r="G66" s="11">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A67" s="8">
+        <v>46084</v>
+      </c>
+      <c r="B67" s="8">
+        <v>46084</v>
+      </c>
+      <c r="C67" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E67" s="11">
+        <v>37</v>
+      </c>
+      <c r="F67" s="11">
+        <v>37</v>
+      </c>
+      <c r="G67" s="11">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A68" s="8">
+        <v>46085</v>
+      </c>
+      <c r="B68" s="8">
+        <v>46085</v>
+      </c>
+      <c r="C68" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D68" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E68" s="11">
+        <v>37</v>
+      </c>
+      <c r="F68" s="11">
+        <v>37</v>
+      </c>
+      <c r="G68" s="11">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A69" s="8">
+        <v>46086</v>
+      </c>
+      <c r="B69" s="8">
+        <v>46086</v>
+      </c>
+      <c r="C69" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D69" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E69" s="11">
+        <v>37</v>
+      </c>
+      <c r="F69" s="11">
+        <v>37</v>
+      </c>
+      <c r="G69" s="11">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A70" s="8">
+        <v>46087</v>
+      </c>
+      <c r="B70" s="8">
+        <v>46087</v>
+      </c>
+      <c r="C70" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D70" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E70" s="11">
+        <v>38</v>
+      </c>
+      <c r="F70" s="11">
+        <v>38</v>
+      </c>
+      <c r="G70" s="11">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A71" s="8">
+        <v>46090</v>
+      </c>
+      <c r="B71" s="8">
+        <v>46090</v>
+      </c>
+      <c r="C71" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D71" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E71" s="11">
+        <v>38</v>
+      </c>
+      <c r="F71" s="11">
+        <v>38</v>
+      </c>
+      <c r="G71" s="11">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A72" s="8">
+        <v>46091</v>
+      </c>
+      <c r="B72" s="8">
+        <v>46091</v>
+      </c>
+      <c r="C72" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D72" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E72" s="11">
+        <v>38</v>
+      </c>
+      <c r="F72" s="11">
+        <v>38</v>
+      </c>
+      <c r="G72" s="11">
+        <v>38</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13725,7 +16600,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD2559E0-BF80-8D49-A825-36795DBC5AE8}">
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:H72"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.6640625" style="8" bestFit="1" customWidth="1"/>
@@ -14863,6 +17738,581 @@
         <v>19</v>
       </c>
     </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A48" s="8">
+        <v>46050</v>
+      </c>
+      <c r="B48" s="8">
+        <v>46050</v>
+      </c>
+      <c r="C48" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="11">
+        <v>19</v>
+      </c>
+      <c r="F48" s="11">
+        <v>19</v>
+      </c>
+      <c r="G48" s="11">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A49" s="8">
+        <v>46051</v>
+      </c>
+      <c r="B49" s="8">
+        <v>46051</v>
+      </c>
+      <c r="C49" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="11">
+        <v>19</v>
+      </c>
+      <c r="F49" s="11">
+        <v>19</v>
+      </c>
+      <c r="G49" s="11">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A50" s="8">
+        <v>46052</v>
+      </c>
+      <c r="B50" s="8">
+        <v>46052</v>
+      </c>
+      <c r="C50" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="11">
+        <v>19</v>
+      </c>
+      <c r="F50" s="11">
+        <v>19</v>
+      </c>
+      <c r="G50" s="11">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A51" s="8">
+        <v>46055</v>
+      </c>
+      <c r="B51" s="8">
+        <v>46055</v>
+      </c>
+      <c r="C51" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" s="11">
+        <v>19</v>
+      </c>
+      <c r="F51" s="11">
+        <v>19</v>
+      </c>
+      <c r="G51" s="11">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A52" s="8">
+        <v>46056</v>
+      </c>
+      <c r="B52" s="8">
+        <v>46056</v>
+      </c>
+      <c r="C52" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="11">
+        <v>19</v>
+      </c>
+      <c r="F52" s="11">
+        <v>19</v>
+      </c>
+      <c r="G52" s="11">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A53" s="8">
+        <v>46057</v>
+      </c>
+      <c r="B53" s="8">
+        <v>46057</v>
+      </c>
+      <c r="C53" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E53" s="11">
+        <v>19</v>
+      </c>
+      <c r="F53" s="11">
+        <v>19</v>
+      </c>
+      <c r="G53" s="11">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="8">
+        <v>46058</v>
+      </c>
+      <c r="B54" s="8">
+        <v>46058</v>
+      </c>
+      <c r="C54" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="11">
+        <v>19</v>
+      </c>
+      <c r="F54" s="11">
+        <v>19</v>
+      </c>
+      <c r="G54" s="11">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="8">
+        <v>46059</v>
+      </c>
+      <c r="B55" s="8">
+        <v>46059</v>
+      </c>
+      <c r="C55" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="11">
+        <v>19</v>
+      </c>
+      <c r="F55" s="11">
+        <v>19</v>
+      </c>
+      <c r="G55" s="11">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="8">
+        <v>46062</v>
+      </c>
+      <c r="B56" s="8">
+        <v>46062</v>
+      </c>
+      <c r="C56" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="11">
+        <v>19.5</v>
+      </c>
+      <c r="F56" s="11">
+        <v>19.5</v>
+      </c>
+      <c r="G56" s="11">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="8">
+        <v>46063</v>
+      </c>
+      <c r="B57" s="8">
+        <v>46063</v>
+      </c>
+      <c r="C57" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="11">
+        <v>19.5</v>
+      </c>
+      <c r="F57" s="11">
+        <v>19.5</v>
+      </c>
+      <c r="G57" s="11">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="8">
+        <v>46064</v>
+      </c>
+      <c r="B58" s="8">
+        <v>46064</v>
+      </c>
+      <c r="C58" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="11">
+        <v>19.5</v>
+      </c>
+      <c r="F58" s="11">
+        <v>19.5</v>
+      </c>
+      <c r="G58" s="11">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="8">
+        <v>46065</v>
+      </c>
+      <c r="B59" s="8">
+        <v>46065</v>
+      </c>
+      <c r="C59" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="11">
+        <v>19.5</v>
+      </c>
+      <c r="F59" s="11">
+        <v>19.5</v>
+      </c>
+      <c r="G59" s="11">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="8">
+        <v>46066</v>
+      </c>
+      <c r="B60" s="8">
+        <v>46066</v>
+      </c>
+      <c r="C60" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D60" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="11">
+        <v>19.5</v>
+      </c>
+      <c r="F60" s="11">
+        <v>19.5</v>
+      </c>
+      <c r="G60" s="11">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A61" s="8">
+        <v>46067</v>
+      </c>
+      <c r="B61" s="8">
+        <v>46067</v>
+      </c>
+      <c r="C61" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D61" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E61" s="11">
+        <v>19.5</v>
+      </c>
+      <c r="F61" s="11">
+        <v>19.5</v>
+      </c>
+      <c r="G61" s="11">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A62" s="8">
+        <v>46077</v>
+      </c>
+      <c r="B62" s="8">
+        <v>46077</v>
+      </c>
+      <c r="C62" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D62" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E62" s="11">
+        <v>19.5</v>
+      </c>
+      <c r="F62" s="11">
+        <v>19.5</v>
+      </c>
+      <c r="G62" s="11">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A63" s="8">
+        <v>46078</v>
+      </c>
+      <c r="B63" s="8">
+        <v>46078</v>
+      </c>
+      <c r="C63" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D63" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E63" s="11">
+        <v>19.5</v>
+      </c>
+      <c r="F63" s="11">
+        <v>19.5</v>
+      </c>
+      <c r="G63" s="11">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A64" s="8">
+        <v>46079</v>
+      </c>
+      <c r="B64" s="8">
+        <v>46079</v>
+      </c>
+      <c r="C64" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D64" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E64" s="11">
+        <v>19.5</v>
+      </c>
+      <c r="F64" s="11">
+        <v>19.5</v>
+      </c>
+      <c r="G64" s="11">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A65" s="8">
+        <v>46080</v>
+      </c>
+      <c r="B65" s="8">
+        <v>46080</v>
+      </c>
+      <c r="C65" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D65" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E65" s="11">
+        <v>19.5</v>
+      </c>
+      <c r="F65" s="11">
+        <v>19.5</v>
+      </c>
+      <c r="G65" s="11">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A66" s="8">
+        <v>46083</v>
+      </c>
+      <c r="B66" s="8">
+        <v>46083</v>
+      </c>
+      <c r="C66" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D66" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E66" s="11">
+        <v>19.5</v>
+      </c>
+      <c r="F66" s="11">
+        <v>19.5</v>
+      </c>
+      <c r="G66" s="11">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A67" s="8">
+        <v>46084</v>
+      </c>
+      <c r="B67" s="8">
+        <v>46084</v>
+      </c>
+      <c r="C67" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E67" s="11">
+        <v>19.5</v>
+      </c>
+      <c r="F67" s="11">
+        <v>19.5</v>
+      </c>
+      <c r="G67" s="11">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A68" s="8">
+        <v>46085</v>
+      </c>
+      <c r="B68" s="8">
+        <v>46085</v>
+      </c>
+      <c r="C68" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D68" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E68" s="11">
+        <v>19.5</v>
+      </c>
+      <c r="F68" s="11">
+        <v>19.5</v>
+      </c>
+      <c r="G68" s="11">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A69" s="8">
+        <v>46086</v>
+      </c>
+      <c r="B69" s="8">
+        <v>46086</v>
+      </c>
+      <c r="C69" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D69" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E69" s="11">
+        <v>19.5</v>
+      </c>
+      <c r="F69" s="11">
+        <v>19.5</v>
+      </c>
+      <c r="G69" s="11">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A70" s="8">
+        <v>46087</v>
+      </c>
+      <c r="B70" s="8">
+        <v>46087</v>
+      </c>
+      <c r="C70" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D70" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E70" s="11">
+        <v>21.5</v>
+      </c>
+      <c r="F70" s="11">
+        <v>21.5</v>
+      </c>
+      <c r="G70" s="11">
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A71" s="8">
+        <v>46090</v>
+      </c>
+      <c r="B71" s="8">
+        <v>46090</v>
+      </c>
+      <c r="C71" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D71" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E71" s="11">
+        <v>24</v>
+      </c>
+      <c r="F71" s="11">
+        <v>24</v>
+      </c>
+      <c r="G71" s="11">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A72" s="8">
+        <v>46091</v>
+      </c>
+      <c r="B72" s="8">
+        <v>46091</v>
+      </c>
+      <c r="C72" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D72" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E72" s="11">
+        <v>24</v>
+      </c>
+      <c r="F72" s="11">
+        <v>24</v>
+      </c>
+      <c r="G72" s="11">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14871,7 +18321,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9243ABC-FEC6-A34B-8298-85FBF7652B6D}">
-  <dimension ref="A1:H125"/>
+  <dimension ref="A1:H150"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.6640625" style="8" bestFit="1" customWidth="1"/>
@@ -17881,6 +21331,581 @@
         <v>27</v>
       </c>
     </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A126" s="8">
+        <v>46050</v>
+      </c>
+      <c r="B126" s="8">
+        <v>46050</v>
+      </c>
+      <c r="C126" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D126" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E126" s="11">
+        <v>27</v>
+      </c>
+      <c r="F126" s="11">
+        <v>27</v>
+      </c>
+      <c r="G126" s="11">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A127" s="8">
+        <v>46051</v>
+      </c>
+      <c r="B127" s="8">
+        <v>46051</v>
+      </c>
+      <c r="C127" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D127" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E127" s="11">
+        <v>27</v>
+      </c>
+      <c r="F127" s="11">
+        <v>27</v>
+      </c>
+      <c r="G127" s="11">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A128" s="8">
+        <v>46052</v>
+      </c>
+      <c r="B128" s="8">
+        <v>46052</v>
+      </c>
+      <c r="C128" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D128" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E128" s="11">
+        <v>27</v>
+      </c>
+      <c r="F128" s="11">
+        <v>27</v>
+      </c>
+      <c r="G128" s="11">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A129" s="8">
+        <v>46055</v>
+      </c>
+      <c r="B129" s="8">
+        <v>46055</v>
+      </c>
+      <c r="C129" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D129" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E129" s="11">
+        <v>27</v>
+      </c>
+      <c r="F129" s="11">
+        <v>27</v>
+      </c>
+      <c r="G129" s="11">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A130" s="8">
+        <v>46056</v>
+      </c>
+      <c r="B130" s="8">
+        <v>46056</v>
+      </c>
+      <c r="C130" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D130" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E130" s="11">
+        <v>27</v>
+      </c>
+      <c r="F130" s="11">
+        <v>27</v>
+      </c>
+      <c r="G130" s="11">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A131" s="8">
+        <v>46057</v>
+      </c>
+      <c r="B131" s="8">
+        <v>46057</v>
+      </c>
+      <c r="C131" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D131" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E131" s="11">
+        <v>27</v>
+      </c>
+      <c r="F131" s="11">
+        <v>27</v>
+      </c>
+      <c r="G131" s="11">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A132" s="8">
+        <v>46058</v>
+      </c>
+      <c r="B132" s="8">
+        <v>46058</v>
+      </c>
+      <c r="C132" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D132" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E132" s="11">
+        <v>27</v>
+      </c>
+      <c r="F132" s="11">
+        <v>27</v>
+      </c>
+      <c r="G132" s="11">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A133" s="8">
+        <v>46059</v>
+      </c>
+      <c r="B133" s="8">
+        <v>46059</v>
+      </c>
+      <c r="C133" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D133" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E133" s="11">
+        <v>27</v>
+      </c>
+      <c r="F133" s="11">
+        <v>27</v>
+      </c>
+      <c r="G133" s="11">
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A134" s="8">
+        <v>46062</v>
+      </c>
+      <c r="B134" s="8">
+        <v>46062</v>
+      </c>
+      <c r="C134" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D134" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E134" s="11">
+        <v>28.5</v>
+      </c>
+      <c r="F134" s="11">
+        <v>28.5</v>
+      </c>
+      <c r="G134" s="11">
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A135" s="8">
+        <v>46063</v>
+      </c>
+      <c r="B135" s="8">
+        <v>46063</v>
+      </c>
+      <c r="C135" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D135" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E135" s="11">
+        <v>28.5</v>
+      </c>
+      <c r="F135" s="11">
+        <v>28.5</v>
+      </c>
+      <c r="G135" s="11">
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A136" s="8">
+        <v>46064</v>
+      </c>
+      <c r="B136" s="8">
+        <v>46064</v>
+      </c>
+      <c r="C136" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D136" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E136" s="11">
+        <v>28.5</v>
+      </c>
+      <c r="F136" s="11">
+        <v>28.5</v>
+      </c>
+      <c r="G136" s="11">
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A137" s="8">
+        <v>46065</v>
+      </c>
+      <c r="B137" s="8">
+        <v>46065</v>
+      </c>
+      <c r="C137" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D137" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E137" s="11">
+        <v>28.5</v>
+      </c>
+      <c r="F137" s="11">
+        <v>28.5</v>
+      </c>
+      <c r="G137" s="11">
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A138" s="8">
+        <v>46066</v>
+      </c>
+      <c r="B138" s="8">
+        <v>46066</v>
+      </c>
+      <c r="C138" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D138" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E138" s="11">
+        <v>28.5</v>
+      </c>
+      <c r="F138" s="11">
+        <v>28.5</v>
+      </c>
+      <c r="G138" s="11">
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A139" s="8">
+        <v>46067</v>
+      </c>
+      <c r="B139" s="8">
+        <v>46067</v>
+      </c>
+      <c r="C139" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D139" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E139" s="11">
+        <v>28.5</v>
+      </c>
+      <c r="F139" s="11">
+        <v>28.5</v>
+      </c>
+      <c r="G139" s="11">
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A140" s="8">
+        <v>46077</v>
+      </c>
+      <c r="B140" s="8">
+        <v>46077</v>
+      </c>
+      <c r="C140" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D140" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E140" s="11">
+        <v>28.5</v>
+      </c>
+      <c r="F140" s="11">
+        <v>28.5</v>
+      </c>
+      <c r="G140" s="11">
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A141" s="8">
+        <v>46078</v>
+      </c>
+      <c r="B141" s="8">
+        <v>46078</v>
+      </c>
+      <c r="C141" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D141" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E141" s="11">
+        <v>28.5</v>
+      </c>
+      <c r="F141" s="11">
+        <v>28.5</v>
+      </c>
+      <c r="G141" s="11">
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A142" s="8">
+        <v>46079</v>
+      </c>
+      <c r="B142" s="8">
+        <v>46079</v>
+      </c>
+      <c r="C142" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D142" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E142" s="11">
+        <v>28.5</v>
+      </c>
+      <c r="F142" s="11">
+        <v>28.5</v>
+      </c>
+      <c r="G142" s="11">
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A143" s="8">
+        <v>46080</v>
+      </c>
+      <c r="B143" s="8">
+        <v>46080</v>
+      </c>
+      <c r="C143" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D143" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E143" s="11">
+        <v>28.5</v>
+      </c>
+      <c r="F143" s="11">
+        <v>28.5</v>
+      </c>
+      <c r="G143" s="11">
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A144" s="8">
+        <v>46083</v>
+      </c>
+      <c r="B144" s="8">
+        <v>46083</v>
+      </c>
+      <c r="C144" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D144" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E144" s="11">
+        <v>28.5</v>
+      </c>
+      <c r="F144" s="11">
+        <v>28.5</v>
+      </c>
+      <c r="G144" s="11">
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A145" s="8">
+        <v>46084</v>
+      </c>
+      <c r="B145" s="8">
+        <v>46084</v>
+      </c>
+      <c r="C145" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D145" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E145" s="11">
+        <v>28.5</v>
+      </c>
+      <c r="F145" s="11">
+        <v>28.5</v>
+      </c>
+      <c r="G145" s="11">
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A146" s="8">
+        <v>46085</v>
+      </c>
+      <c r="B146" s="8">
+        <v>46085</v>
+      </c>
+      <c r="C146" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D146" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E146" s="11">
+        <v>28.5</v>
+      </c>
+      <c r="F146" s="11">
+        <v>28.5</v>
+      </c>
+      <c r="G146" s="11">
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A147" s="8">
+        <v>46086</v>
+      </c>
+      <c r="B147" s="8">
+        <v>46086</v>
+      </c>
+      <c r="C147" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D147" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E147" s="11">
+        <v>28.5</v>
+      </c>
+      <c r="F147" s="11">
+        <v>28.5</v>
+      </c>
+      <c r="G147" s="11">
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A148" s="8">
+        <v>46087</v>
+      </c>
+      <c r="B148" s="8">
+        <v>46087</v>
+      </c>
+      <c r="C148" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D148" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E148" s="11">
+        <v>33</v>
+      </c>
+      <c r="F148" s="11">
+        <v>33</v>
+      </c>
+      <c r="G148" s="11">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A149" s="8">
+        <v>46090</v>
+      </c>
+      <c r="B149" s="8">
+        <v>46090</v>
+      </c>
+      <c r="C149" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D149" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E149" s="11">
+        <v>33</v>
+      </c>
+      <c r="F149" s="11">
+        <v>33</v>
+      </c>
+      <c r="G149" s="11">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A150" s="8">
+        <v>46091</v>
+      </c>
+      <c r="B150" s="8">
+        <v>46091</v>
+      </c>
+      <c r="C150" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D150" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E150" s="11">
+        <v>33</v>
+      </c>
+      <c r="F150" s="11">
+        <v>33</v>
+      </c>
+      <c r="G150" s="11">
+        <v>33</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -17889,7 +21914,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBFF5017-E975-3245-B813-D752FBEC2974}">
-  <dimension ref="A1:H125"/>
+  <dimension ref="A1:H150"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.6640625" style="8" bestFit="1" customWidth="1"/>
@@ -20899,6 +24924,581 @@
         <v>55</v>
       </c>
     </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A126" s="8">
+        <v>46050</v>
+      </c>
+      <c r="B126" s="8">
+        <v>46050</v>
+      </c>
+      <c r="C126" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D126" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E126" s="11">
+        <v>55</v>
+      </c>
+      <c r="F126" s="11">
+        <v>55</v>
+      </c>
+      <c r="G126" s="11">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A127" s="8">
+        <v>46051</v>
+      </c>
+      <c r="B127" s="8">
+        <v>46051</v>
+      </c>
+      <c r="C127" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D127" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E127" s="11">
+        <v>55</v>
+      </c>
+      <c r="F127" s="11">
+        <v>55</v>
+      </c>
+      <c r="G127" s="11">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A128" s="8">
+        <v>46052</v>
+      </c>
+      <c r="B128" s="8">
+        <v>46052</v>
+      </c>
+      <c r="C128" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D128" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E128" s="11">
+        <v>55</v>
+      </c>
+      <c r="F128" s="11">
+        <v>55</v>
+      </c>
+      <c r="G128" s="11">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A129" s="8">
+        <v>46055</v>
+      </c>
+      <c r="B129" s="8">
+        <v>46055</v>
+      </c>
+      <c r="C129" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D129" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E129" s="11">
+        <v>55</v>
+      </c>
+      <c r="F129" s="11">
+        <v>55</v>
+      </c>
+      <c r="G129" s="11">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A130" s="8">
+        <v>46056</v>
+      </c>
+      <c r="B130" s="8">
+        <v>46056</v>
+      </c>
+      <c r="C130" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D130" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E130" s="11">
+        <v>55</v>
+      </c>
+      <c r="F130" s="11">
+        <v>55</v>
+      </c>
+      <c r="G130" s="11">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A131" s="8">
+        <v>46057</v>
+      </c>
+      <c r="B131" s="8">
+        <v>46057</v>
+      </c>
+      <c r="C131" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D131" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E131" s="11">
+        <v>55</v>
+      </c>
+      <c r="F131" s="11">
+        <v>55</v>
+      </c>
+      <c r="G131" s="11">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A132" s="8">
+        <v>46058</v>
+      </c>
+      <c r="B132" s="8">
+        <v>46058</v>
+      </c>
+      <c r="C132" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D132" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E132" s="11">
+        <v>55</v>
+      </c>
+      <c r="F132" s="11">
+        <v>55</v>
+      </c>
+      <c r="G132" s="11">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A133" s="8">
+        <v>46059</v>
+      </c>
+      <c r="B133" s="8">
+        <v>46059</v>
+      </c>
+      <c r="C133" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D133" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E133" s="11">
+        <v>55</v>
+      </c>
+      <c r="F133" s="11">
+        <v>55</v>
+      </c>
+      <c r="G133" s="11">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A134" s="8">
+        <v>46062</v>
+      </c>
+      <c r="B134" s="8">
+        <v>46062</v>
+      </c>
+      <c r="C134" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D134" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E134" s="11">
+        <v>55</v>
+      </c>
+      <c r="F134" s="11">
+        <v>55</v>
+      </c>
+      <c r="G134" s="11">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A135" s="8">
+        <v>46063</v>
+      </c>
+      <c r="B135" s="8">
+        <v>46063</v>
+      </c>
+      <c r="C135" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D135" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E135" s="11">
+        <v>55</v>
+      </c>
+      <c r="F135" s="11">
+        <v>55</v>
+      </c>
+      <c r="G135" s="11">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A136" s="8">
+        <v>46064</v>
+      </c>
+      <c r="B136" s="8">
+        <v>46064</v>
+      </c>
+      <c r="C136" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D136" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E136" s="11">
+        <v>55</v>
+      </c>
+      <c r="F136" s="11">
+        <v>55</v>
+      </c>
+      <c r="G136" s="11">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A137" s="8">
+        <v>46065</v>
+      </c>
+      <c r="B137" s="8">
+        <v>46065</v>
+      </c>
+      <c r="C137" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D137" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E137" s="11">
+        <v>55</v>
+      </c>
+      <c r="F137" s="11">
+        <v>55</v>
+      </c>
+      <c r="G137" s="11">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A138" s="8">
+        <v>46066</v>
+      </c>
+      <c r="B138" s="8">
+        <v>46066</v>
+      </c>
+      <c r="C138" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D138" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E138" s="11">
+        <v>55</v>
+      </c>
+      <c r="F138" s="11">
+        <v>55</v>
+      </c>
+      <c r="G138" s="11">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A139" s="8">
+        <v>46067</v>
+      </c>
+      <c r="B139" s="8">
+        <v>46067</v>
+      </c>
+      <c r="C139" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D139" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E139" s="11">
+        <v>55</v>
+      </c>
+      <c r="F139" s="11">
+        <v>55</v>
+      </c>
+      <c r="G139" s="11">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A140" s="8">
+        <v>46077</v>
+      </c>
+      <c r="B140" s="8">
+        <v>46077</v>
+      </c>
+      <c r="C140" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D140" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E140" s="11">
+        <v>55</v>
+      </c>
+      <c r="F140" s="11">
+        <v>55</v>
+      </c>
+      <c r="G140" s="11">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A141" s="8">
+        <v>46078</v>
+      </c>
+      <c r="B141" s="8">
+        <v>46078</v>
+      </c>
+      <c r="C141" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D141" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E141" s="11">
+        <v>55</v>
+      </c>
+      <c r="F141" s="11">
+        <v>55</v>
+      </c>
+      <c r="G141" s="11">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A142" s="8">
+        <v>46079</v>
+      </c>
+      <c r="B142" s="8">
+        <v>46079</v>
+      </c>
+      <c r="C142" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D142" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E142" s="11">
+        <v>55</v>
+      </c>
+      <c r="F142" s="11">
+        <v>55</v>
+      </c>
+      <c r="G142" s="11">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A143" s="8">
+        <v>46080</v>
+      </c>
+      <c r="B143" s="8">
+        <v>46080</v>
+      </c>
+      <c r="C143" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D143" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E143" s="11">
+        <v>55</v>
+      </c>
+      <c r="F143" s="11">
+        <v>55</v>
+      </c>
+      <c r="G143" s="11">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A144" s="8">
+        <v>46083</v>
+      </c>
+      <c r="B144" s="8">
+        <v>46083</v>
+      </c>
+      <c r="C144" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D144" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E144" s="11">
+        <v>55</v>
+      </c>
+      <c r="F144" s="11">
+        <v>55</v>
+      </c>
+      <c r="G144" s="11">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A145" s="8">
+        <v>46084</v>
+      </c>
+      <c r="B145" s="8">
+        <v>46084</v>
+      </c>
+      <c r="C145" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D145" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E145" s="11">
+        <v>55</v>
+      </c>
+      <c r="F145" s="11">
+        <v>55</v>
+      </c>
+      <c r="G145" s="11">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A146" s="8">
+        <v>46085</v>
+      </c>
+      <c r="B146" s="8">
+        <v>46085</v>
+      </c>
+      <c r="C146" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D146" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E146" s="11">
+        <v>55</v>
+      </c>
+      <c r="F146" s="11">
+        <v>55</v>
+      </c>
+      <c r="G146" s="11">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A147" s="8">
+        <v>46086</v>
+      </c>
+      <c r="B147" s="8">
+        <v>46086</v>
+      </c>
+      <c r="C147" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D147" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E147" s="11">
+        <v>55</v>
+      </c>
+      <c r="F147" s="11">
+        <v>55</v>
+      </c>
+      <c r="G147" s="11">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A148" s="8">
+        <v>46087</v>
+      </c>
+      <c r="B148" s="8">
+        <v>46087</v>
+      </c>
+      <c r="C148" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D148" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E148" s="11">
+        <v>58</v>
+      </c>
+      <c r="F148" s="11">
+        <v>58</v>
+      </c>
+      <c r="G148" s="11">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A149" s="8">
+        <v>46090</v>
+      </c>
+      <c r="B149" s="8">
+        <v>46090</v>
+      </c>
+      <c r="C149" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D149" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E149" s="11">
+        <v>61</v>
+      </c>
+      <c r="F149" s="11">
+        <v>61</v>
+      </c>
+      <c r="G149" s="11">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A150" s="8">
+        <v>46091</v>
+      </c>
+      <c r="B150" s="8">
+        <v>46091</v>
+      </c>
+      <c r="C150" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D150" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E150" s="11">
+        <v>61</v>
+      </c>
+      <c r="F150" s="11">
+        <v>61</v>
+      </c>
+      <c r="G150" s="11">
+        <v>61</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -20907,7 +25507,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14E7EEF0-A0B2-3A49-9389-9D8B09E58931}">
-  <dimension ref="A1:H125"/>
+  <dimension ref="A1:H150"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.6640625" style="8" bestFit="1" customWidth="1"/>
@@ -23917,6 +28517,581 @@
         <v>94</v>
       </c>
     </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A126" s="8">
+        <v>46050</v>
+      </c>
+      <c r="B126" s="8">
+        <v>46050</v>
+      </c>
+      <c r="C126" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D126" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E126" s="11">
+        <v>94</v>
+      </c>
+      <c r="F126" s="11">
+        <v>94</v>
+      </c>
+      <c r="G126" s="11">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A127" s="8">
+        <v>46051</v>
+      </c>
+      <c r="B127" s="8">
+        <v>46051</v>
+      </c>
+      <c r="C127" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D127" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E127" s="11">
+        <v>94</v>
+      </c>
+      <c r="F127" s="11">
+        <v>94</v>
+      </c>
+      <c r="G127" s="11">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A128" s="8">
+        <v>46052</v>
+      </c>
+      <c r="B128" s="8">
+        <v>46052</v>
+      </c>
+      <c r="C128" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D128" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E128" s="11">
+        <v>94</v>
+      </c>
+      <c r="F128" s="11">
+        <v>94</v>
+      </c>
+      <c r="G128" s="11">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A129" s="8">
+        <v>46055</v>
+      </c>
+      <c r="B129" s="8">
+        <v>46055</v>
+      </c>
+      <c r="C129" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D129" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E129" s="11">
+        <v>94</v>
+      </c>
+      <c r="F129" s="11">
+        <v>94</v>
+      </c>
+      <c r="G129" s="11">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A130" s="8">
+        <v>46056</v>
+      </c>
+      <c r="B130" s="8">
+        <v>46056</v>
+      </c>
+      <c r="C130" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D130" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E130" s="11">
+        <v>94</v>
+      </c>
+      <c r="F130" s="11">
+        <v>94</v>
+      </c>
+      <c r="G130" s="11">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A131" s="8">
+        <v>46057</v>
+      </c>
+      <c r="B131" s="8">
+        <v>46057</v>
+      </c>
+      <c r="C131" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D131" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E131" s="11">
+        <v>94</v>
+      </c>
+      <c r="F131" s="11">
+        <v>94</v>
+      </c>
+      <c r="G131" s="11">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A132" s="8">
+        <v>46058</v>
+      </c>
+      <c r="B132" s="8">
+        <v>46058</v>
+      </c>
+      <c r="C132" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D132" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E132" s="11">
+        <v>94</v>
+      </c>
+      <c r="F132" s="11">
+        <v>94</v>
+      </c>
+      <c r="G132" s="11">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A133" s="8">
+        <v>46059</v>
+      </c>
+      <c r="B133" s="8">
+        <v>46059</v>
+      </c>
+      <c r="C133" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D133" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E133" s="11">
+        <v>94</v>
+      </c>
+      <c r="F133" s="11">
+        <v>94</v>
+      </c>
+      <c r="G133" s="11">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A134" s="8">
+        <v>46062</v>
+      </c>
+      <c r="B134" s="8">
+        <v>46062</v>
+      </c>
+      <c r="C134" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D134" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E134" s="11">
+        <v>96</v>
+      </c>
+      <c r="F134" s="11">
+        <v>96</v>
+      </c>
+      <c r="G134" s="11">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A135" s="8">
+        <v>46063</v>
+      </c>
+      <c r="B135" s="8">
+        <v>46063</v>
+      </c>
+      <c r="C135" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D135" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E135" s="11">
+        <v>96</v>
+      </c>
+      <c r="F135" s="11">
+        <v>96</v>
+      </c>
+      <c r="G135" s="11">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A136" s="8">
+        <v>46064</v>
+      </c>
+      <c r="B136" s="8">
+        <v>46064</v>
+      </c>
+      <c r="C136" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D136" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E136" s="11">
+        <v>96</v>
+      </c>
+      <c r="F136" s="11">
+        <v>96</v>
+      </c>
+      <c r="G136" s="11">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A137" s="8">
+        <v>46065</v>
+      </c>
+      <c r="B137" s="8">
+        <v>46065</v>
+      </c>
+      <c r="C137" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D137" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E137" s="11">
+        <v>96</v>
+      </c>
+      <c r="F137" s="11">
+        <v>96</v>
+      </c>
+      <c r="G137" s="11">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A138" s="8">
+        <v>46066</v>
+      </c>
+      <c r="B138" s="8">
+        <v>46066</v>
+      </c>
+      <c r="C138" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D138" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E138" s="11">
+        <v>96</v>
+      </c>
+      <c r="F138" s="11">
+        <v>96</v>
+      </c>
+      <c r="G138" s="11">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A139" s="8">
+        <v>46067</v>
+      </c>
+      <c r="B139" s="8">
+        <v>46067</v>
+      </c>
+      <c r="C139" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D139" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E139" s="11">
+        <v>96</v>
+      </c>
+      <c r="F139" s="11">
+        <v>96</v>
+      </c>
+      <c r="G139" s="11">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A140" s="8">
+        <v>46077</v>
+      </c>
+      <c r="B140" s="8">
+        <v>46077</v>
+      </c>
+      <c r="C140" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D140" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E140" s="11">
+        <v>96</v>
+      </c>
+      <c r="F140" s="11">
+        <v>96</v>
+      </c>
+      <c r="G140" s="11">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A141" s="8">
+        <v>46078</v>
+      </c>
+      <c r="B141" s="8">
+        <v>46078</v>
+      </c>
+      <c r="C141" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D141" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E141" s="11">
+        <v>96</v>
+      </c>
+      <c r="F141" s="11">
+        <v>96</v>
+      </c>
+      <c r="G141" s="11">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A142" s="8">
+        <v>46079</v>
+      </c>
+      <c r="B142" s="8">
+        <v>46079</v>
+      </c>
+      <c r="C142" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D142" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E142" s="11">
+        <v>96</v>
+      </c>
+      <c r="F142" s="11">
+        <v>96</v>
+      </c>
+      <c r="G142" s="11">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A143" s="8">
+        <v>46080</v>
+      </c>
+      <c r="B143" s="8">
+        <v>46080</v>
+      </c>
+      <c r="C143" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D143" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E143" s="11">
+        <v>96</v>
+      </c>
+      <c r="F143" s="11">
+        <v>96</v>
+      </c>
+      <c r="G143" s="11">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A144" s="8">
+        <v>46083</v>
+      </c>
+      <c r="B144" s="8">
+        <v>46083</v>
+      </c>
+      <c r="C144" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D144" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E144" s="11">
+        <v>96</v>
+      </c>
+      <c r="F144" s="11">
+        <v>96</v>
+      </c>
+      <c r="G144" s="11">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A145" s="8">
+        <v>46084</v>
+      </c>
+      <c r="B145" s="8">
+        <v>46084</v>
+      </c>
+      <c r="C145" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D145" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E145" s="11">
+        <v>96</v>
+      </c>
+      <c r="F145" s="11">
+        <v>96</v>
+      </c>
+      <c r="G145" s="11">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A146" s="8">
+        <v>46085</v>
+      </c>
+      <c r="B146" s="8">
+        <v>46085</v>
+      </c>
+      <c r="C146" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D146" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E146" s="11">
+        <v>96</v>
+      </c>
+      <c r="F146" s="11">
+        <v>96</v>
+      </c>
+      <c r="G146" s="11">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A147" s="8">
+        <v>46086</v>
+      </c>
+      <c r="B147" s="8">
+        <v>46086</v>
+      </c>
+      <c r="C147" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D147" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E147" s="11">
+        <v>96</v>
+      </c>
+      <c r="F147" s="11">
+        <v>96</v>
+      </c>
+      <c r="G147" s="11">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A148" s="8">
+        <v>46087</v>
+      </c>
+      <c r="B148" s="8">
+        <v>46087</v>
+      </c>
+      <c r="C148" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D148" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E148" s="11">
+        <v>105</v>
+      </c>
+      <c r="F148" s="11">
+        <v>105</v>
+      </c>
+      <c r="G148" s="11">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A149" s="8">
+        <v>46090</v>
+      </c>
+      <c r="B149" s="8">
+        <v>46090</v>
+      </c>
+      <c r="C149" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D149" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E149" s="11">
+        <v>120</v>
+      </c>
+      <c r="F149" s="11">
+        <v>120</v>
+      </c>
+      <c r="G149" s="11">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A150" s="8">
+        <v>46091</v>
+      </c>
+      <c r="B150" s="8">
+        <v>46091</v>
+      </c>
+      <c r="C150" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D150" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E150" s="11">
+        <v>120</v>
+      </c>
+      <c r="F150" s="11">
+        <v>120</v>
+      </c>
+      <c r="G150" s="11">
+        <v>120</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/industry/CFM/Flash Card.xlsx
+++ b/data/industry/CFM/Flash Card.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{242E51EE-9532-45AF-ADFA-0133600BAE83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47964972-195B-4066-BEF9-93D154A90AA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="767" xr2:uid="{9A28822D-BA55-F242-829D-3FA5BE3F147C}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1509" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1540" uniqueCount="9">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="0" type="noConversion"/>
@@ -85,23 +85,23 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="179" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -120,13 +120,13 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Aptos Narrow"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -151,37 +151,37 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="쉼표" xfId="1" builtinId="3"/>
@@ -240,10 +240,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'MicroSD 16GB(Channel)'!$B$2:$B$1165</c:f>
+              <c:f>'MicroSD 16GB(Channel)'!$B$2:$B$1148</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="1164"/>
+                <c:ptCount val="1147"/>
                 <c:pt idx="0">
                   <c:v>45866</c:v>
                 </c:pt>
@@ -777,16 +777,109 @@
                 </c:pt>
                 <c:pt idx="177">
                   <c:v>46135</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>46136</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>46139</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>46140</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>46141</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>46148</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>46149</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>46150</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>46153</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>46154</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>46155</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>46156</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>46157</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>46160</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>46161</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>46162</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>46163</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>46164</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>46167</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>46168</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>46169</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>46170</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>46174</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>46175</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>46176</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>46177</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>46178</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>46181</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>46182</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>46183</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'MicroSD 16GB(Channel)'!$G$2:$G$1165</c:f>
+              <c:f>'MicroSD 16GB(Channel)'!$G$2:$G$1148</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0.0_);_(* \(#,##0.0\);_(* "-"??_);_(@_)</c:formatCode>
-                <c:ptCount val="1164"/>
+                <c:ptCount val="1147"/>
                 <c:pt idx="0">
                   <c:v>1.2</c:v>
                 </c:pt>
@@ -1320,6 +1413,99 @@
                 </c:pt>
                 <c:pt idx="177">
                   <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>3.3</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>3.3</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>3.3</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>3.3</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>3.3</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>3.2</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>3.2</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>3.2</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>3.2</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>3.2</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>3.2</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>3.2</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>3.2</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>3.2</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>3.2</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>3.2</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>3.2</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>3.2</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>3.2</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>3.2</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>3.2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5004,10 +5190,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'MicroSD 16GB(Channel)'!$B$2:$B$1165</c:f>
+              <c:f>'MicroSD 16GB(Channel)'!$B$2:$B$1148</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="1164"/>
+                <c:ptCount val="1147"/>
                 <c:pt idx="0">
                   <c:v>45866</c:v>
                 </c:pt>
@@ -5541,6 +5727,99 @@
                 </c:pt>
                 <c:pt idx="177">
                   <c:v>46135</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>46136</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>46139</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>46140</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>46141</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>46148</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>46149</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>46150</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>46153</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>46154</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>46155</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>46156</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>46157</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>46160</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>46161</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>46162</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>46163</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>46164</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>46167</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>46168</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>46169</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>46170</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>46174</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>46175</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>46176</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>46177</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>46178</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>46181</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>46182</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>46183</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10130,15 +10409,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B272F1F1-C221-BA47-B841-D5FD2627A973}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:H179"/>
+  <dimension ref="A1:H210"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.6328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.09765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="11"/>
-    <col min="7" max="7" width="11.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.09765625" style="11" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -14376,10 +14655,723 @@
         <v>3.5</v>
       </c>
       <c r="F179" s="11">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="G179" s="11">
         <v>3.5</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A180" s="8">
+        <v>46136</v>
+      </c>
+      <c r="B180" s="8">
+        <v>46136</v>
+      </c>
+      <c r="C180" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D180" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E180" s="11">
+        <v>3.5</v>
+      </c>
+      <c r="F180" s="11">
+        <v>3.5</v>
+      </c>
+      <c r="G180" s="11">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A181" s="8">
+        <v>46139</v>
+      </c>
+      <c r="B181" s="8">
+        <v>46139</v>
+      </c>
+      <c r="C181" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D181" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E181" s="11">
+        <v>3.5</v>
+      </c>
+      <c r="F181" s="11">
+        <v>3.5</v>
+      </c>
+      <c r="G181" s="11">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A182" s="8">
+        <v>46140</v>
+      </c>
+      <c r="B182" s="8">
+        <v>46140</v>
+      </c>
+      <c r="C182" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D182" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E182" s="11">
+        <v>3.5</v>
+      </c>
+      <c r="F182" s="11">
+        <v>3.5</v>
+      </c>
+      <c r="G182" s="11">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A183" s="8">
+        <v>46141</v>
+      </c>
+      <c r="B183" s="8">
+        <v>46141</v>
+      </c>
+      <c r="C183" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D183" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E183" s="11">
+        <v>3.5</v>
+      </c>
+      <c r="F183" s="11">
+        <v>3.5</v>
+      </c>
+      <c r="G183" s="11">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A184" s="8">
+        <v>46142</v>
+      </c>
+      <c r="B184" s="8">
+        <v>46142</v>
+      </c>
+      <c r="C184" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D184" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E184" s="11">
+        <v>3.5</v>
+      </c>
+      <c r="F184" s="11">
+        <v>3.5</v>
+      </c>
+      <c r="G184" s="11">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A185" s="8">
+        <v>46148</v>
+      </c>
+      <c r="B185" s="8">
+        <v>46148</v>
+      </c>
+      <c r="C185" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D185" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E185" s="11">
+        <v>3.5</v>
+      </c>
+      <c r="F185" s="11">
+        <v>3.5</v>
+      </c>
+      <c r="G185" s="11">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A186" s="8">
+        <v>46149</v>
+      </c>
+      <c r="B186" s="8">
+        <v>46149</v>
+      </c>
+      <c r="C186" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D186" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E186" s="11">
+        <v>3.5</v>
+      </c>
+      <c r="F186" s="11">
+        <v>3.5</v>
+      </c>
+      <c r="G186" s="11">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A187" s="8">
+        <v>46150</v>
+      </c>
+      <c r="B187" s="8">
+        <v>46150</v>
+      </c>
+      <c r="C187" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D187" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E187" s="11">
+        <v>3.5</v>
+      </c>
+      <c r="F187" s="11">
+        <v>3.5</v>
+      </c>
+      <c r="G187" s="11">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A188" s="8">
+        <v>46153</v>
+      </c>
+      <c r="B188" s="8">
+        <v>46153</v>
+      </c>
+      <c r="C188" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D188" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E188" s="11">
+        <v>3.5</v>
+      </c>
+      <c r="F188" s="11">
+        <v>3.5</v>
+      </c>
+      <c r="G188" s="11">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A189" s="8">
+        <v>46154</v>
+      </c>
+      <c r="B189" s="8">
+        <v>46154</v>
+      </c>
+      <c r="C189" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D189" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E189" s="11">
+        <v>3.5</v>
+      </c>
+      <c r="F189" s="11">
+        <v>3.5</v>
+      </c>
+      <c r="G189" s="11">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A190" s="8">
+        <v>46155</v>
+      </c>
+      <c r="B190" s="8">
+        <v>46155</v>
+      </c>
+      <c r="C190" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D190" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E190" s="11">
+        <v>3.3</v>
+      </c>
+      <c r="F190" s="11">
+        <v>3.3</v>
+      </c>
+      <c r="G190" s="11">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A191" s="8">
+        <v>46156</v>
+      </c>
+      <c r="B191" s="8">
+        <v>46156</v>
+      </c>
+      <c r="C191" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D191" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E191" s="11">
+        <v>3.3</v>
+      </c>
+      <c r="F191" s="11">
+        <v>3.3</v>
+      </c>
+      <c r="G191" s="11">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A192" s="8">
+        <v>46157</v>
+      </c>
+      <c r="B192" s="8">
+        <v>46157</v>
+      </c>
+      <c r="C192" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D192" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E192" s="11">
+        <v>3.3</v>
+      </c>
+      <c r="F192" s="11">
+        <v>3.3</v>
+      </c>
+      <c r="G192" s="11">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A193" s="8">
+        <v>46160</v>
+      </c>
+      <c r="B193" s="8">
+        <v>46160</v>
+      </c>
+      <c r="C193" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D193" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E193" s="11">
+        <v>3.3</v>
+      </c>
+      <c r="F193" s="11">
+        <v>3.3</v>
+      </c>
+      <c r="G193" s="11">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A194" s="8">
+        <v>46161</v>
+      </c>
+      <c r="B194" s="8">
+        <v>46161</v>
+      </c>
+      <c r="C194" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D194" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E194" s="11">
+        <v>3.3</v>
+      </c>
+      <c r="F194" s="11">
+        <v>3.3</v>
+      </c>
+      <c r="G194" s="11">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A195" s="8">
+        <v>46162</v>
+      </c>
+      <c r="B195" s="8">
+        <v>46162</v>
+      </c>
+      <c r="C195" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D195" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E195" s="11">
+        <v>3.2</v>
+      </c>
+      <c r="F195" s="11">
+        <v>3.2</v>
+      </c>
+      <c r="G195" s="11">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A196" s="8">
+        <v>46163</v>
+      </c>
+      <c r="B196" s="8">
+        <v>46163</v>
+      </c>
+      <c r="C196" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D196" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E196" s="11">
+        <v>3.2</v>
+      </c>
+      <c r="F196" s="11">
+        <v>3.2</v>
+      </c>
+      <c r="G196" s="11">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A197" s="8">
+        <v>46164</v>
+      </c>
+      <c r="B197" s="8">
+        <v>46164</v>
+      </c>
+      <c r="C197" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D197" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E197" s="11">
+        <v>3.2</v>
+      </c>
+      <c r="F197" s="11">
+        <v>3.2</v>
+      </c>
+      <c r="G197" s="11">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A198" s="8">
+        <v>46167</v>
+      </c>
+      <c r="B198" s="8">
+        <v>46167</v>
+      </c>
+      <c r="C198" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D198" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E198" s="11">
+        <v>3.2</v>
+      </c>
+      <c r="F198" s="11">
+        <v>3.2</v>
+      </c>
+      <c r="G198" s="11">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A199" s="8">
+        <v>46168</v>
+      </c>
+      <c r="B199" s="8">
+        <v>46168</v>
+      </c>
+      <c r="C199" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D199" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E199" s="11">
+        <v>3.2</v>
+      </c>
+      <c r="F199" s="11">
+        <v>3.2</v>
+      </c>
+      <c r="G199" s="11">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A200" s="8">
+        <v>46169</v>
+      </c>
+      <c r="B200" s="8">
+        <v>46169</v>
+      </c>
+      <c r="C200" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D200" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E200" s="11">
+        <v>3.2</v>
+      </c>
+      <c r="F200" s="11">
+        <v>3.2</v>
+      </c>
+      <c r="G200" s="11">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A201" s="8">
+        <v>46170</v>
+      </c>
+      <c r="B201" s="8">
+        <v>46170</v>
+      </c>
+      <c r="C201" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D201" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E201" s="11">
+        <v>3.2</v>
+      </c>
+      <c r="F201" s="11">
+        <v>3.2</v>
+      </c>
+      <c r="G201" s="11">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A202" s="8">
+        <v>46171</v>
+      </c>
+      <c r="B202" s="8">
+        <v>46171</v>
+      </c>
+      <c r="C202" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D202" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E202" s="11">
+        <v>3.2</v>
+      </c>
+      <c r="F202" s="11">
+        <v>3.2</v>
+      </c>
+      <c r="G202" s="11">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A203" s="8">
+        <v>46174</v>
+      </c>
+      <c r="B203" s="8">
+        <v>46174</v>
+      </c>
+      <c r="C203" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D203" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E203" s="11">
+        <v>3.2</v>
+      </c>
+      <c r="F203" s="11">
+        <v>3.2</v>
+      </c>
+      <c r="G203" s="11">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A204" s="8">
+        <v>46175</v>
+      </c>
+      <c r="B204" s="8">
+        <v>46175</v>
+      </c>
+      <c r="C204" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D204" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E204" s="11">
+        <v>3.2</v>
+      </c>
+      <c r="F204" s="11">
+        <v>3.2</v>
+      </c>
+      <c r="G204" s="11">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A205" s="8">
+        <v>46176</v>
+      </c>
+      <c r="B205" s="8">
+        <v>46176</v>
+      </c>
+      <c r="C205" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D205" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E205" s="11">
+        <v>3.2</v>
+      </c>
+      <c r="F205" s="11">
+        <v>3.2</v>
+      </c>
+      <c r="G205" s="11">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A206" s="8">
+        <v>46177</v>
+      </c>
+      <c r="B206" s="8">
+        <v>46177</v>
+      </c>
+      <c r="C206" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D206" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E206" s="11">
+        <v>3.2</v>
+      </c>
+      <c r="F206" s="11">
+        <v>3.2</v>
+      </c>
+      <c r="G206" s="11">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A207" s="8">
+        <v>46178</v>
+      </c>
+      <c r="B207" s="8">
+        <v>46178</v>
+      </c>
+      <c r="C207" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D207" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E207" s="11">
+        <v>3.2</v>
+      </c>
+      <c r="F207" s="11">
+        <v>3.2</v>
+      </c>
+      <c r="G207" s="11">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A208" s="8">
+        <v>46181</v>
+      </c>
+      <c r="B208" s="8">
+        <v>46181</v>
+      </c>
+      <c r="C208" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D208" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E208" s="11">
+        <v>3.2</v>
+      </c>
+      <c r="F208" s="11">
+        <v>3.2</v>
+      </c>
+      <c r="G208" s="11">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A209" s="8">
+        <v>46182</v>
+      </c>
+      <c r="B209" s="8">
+        <v>46182</v>
+      </c>
+      <c r="C209" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D209" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E209" s="11">
+        <v>3.2</v>
+      </c>
+      <c r="F209" s="11">
+        <v>3.2</v>
+      </c>
+      <c r="G209" s="11">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A210" s="8">
+        <v>46183</v>
+      </c>
+      <c r="B210" s="8">
+        <v>46183</v>
+      </c>
+      <c r="C210" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D210" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E210" s="11">
+        <v>3.2</v>
+      </c>
+      <c r="F210" s="11">
+        <v>3.2</v>
+      </c>
+      <c r="G210" s="11">
+        <v>3.2</v>
       </c>
     </row>
   </sheetData>
@@ -14393,7 +15385,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3EFB630-E0BB-4706-9416-36C816E52A8D}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="19.2" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14407,12 +15399,12 @@
   <dimension ref="A1:H179"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.6328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.09765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="11"/>
-    <col min="7" max="7" width="11.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.09765625" style="11" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -18668,12 +19660,12 @@
   <dimension ref="A1:H179"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.6328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.09765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="11"/>
-    <col min="7" max="7" width="11.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.09765625" style="11" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -22929,12 +23921,12 @@
   <dimension ref="A1:H179"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.6328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.09765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="11"/>
-    <col min="7" max="7" width="11.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.09765625" style="11" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -27190,12 +28182,12 @@
   <dimension ref="A1:H101"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.6328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.09765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="11"/>
-    <col min="7" max="7" width="11.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.09765625" style="11" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -29579,12 +30571,12 @@
   <dimension ref="A1:H101"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.6328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.09765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="11"/>
-    <col min="7" max="7" width="11.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.09765625" style="11" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -31968,12 +32960,12 @@
   <dimension ref="A1:H179"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.6328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.09765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="11"/>
-    <col min="7" max="7" width="11.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.09765625" style="11" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -36229,12 +37221,12 @@
   <dimension ref="A1:H179"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.6328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.09765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="11"/>
-    <col min="7" max="7" width="11.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.09765625" style="11" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -40490,12 +41482,12 @@
   <dimension ref="A1:H179"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.6328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.09765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="11"/>
-    <col min="7" max="7" width="11.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.09765625" style="11" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
